--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/63.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/63.xlsx
@@ -426,13 +426,13 @@
         <v>-7.684220939041826</v>
       </c>
       <c r="E2">
-        <v>-15.79127632942211</v>
+        <v>-17.68181812448406</v>
       </c>
       <c r="F2">
-        <v>-2.03062272193709</v>
+        <v>-2.703173387902606</v>
       </c>
       <c r="G2">
-        <v>-4.843788301944243</v>
+        <v>-5.451389501378629</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.035544793438093</v>
       </c>
       <c r="E3">
-        <v>-16.04257468705351</v>
+        <v>-18.50870173320079</v>
       </c>
       <c r="F3">
-        <v>-1.988871348101189</v>
+        <v>-2.58106954762775</v>
       </c>
       <c r="G3">
-        <v>-4.120348365002161</v>
+        <v>-5.08354080997995</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.420016943628578</v>
       </c>
       <c r="E4">
-        <v>-17.19891593732359</v>
+        <v>-18.37464022484665</v>
       </c>
       <c r="F4">
-        <v>-2.008951802312452</v>
+        <v>-2.926568337456979</v>
       </c>
       <c r="G4">
-        <v>-3.505400530288382</v>
+        <v>-4.179304199358681</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.935855415897442</v>
       </c>
       <c r="E5">
-        <v>-17.43775881419183</v>
+        <v>-18.93931498978167</v>
       </c>
       <c r="F5">
-        <v>-2.219907986946388</v>
+        <v>-2.865408315373486</v>
       </c>
       <c r="G5">
-        <v>-1.840189307738595</v>
+        <v>-4.147904774161361</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.569271703863346</v>
       </c>
       <c r="E6">
-        <v>-17.08639298290001</v>
+        <v>-18.3075866280073</v>
       </c>
       <c r="F6">
-        <v>-2.077355068966024</v>
+        <v>-2.848290931362037</v>
       </c>
       <c r="G6">
-        <v>-2.087079591486405</v>
+        <v>-2.847427624713056</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.328678855652923</v>
       </c>
       <c r="E7">
-        <v>-19.01021030709649</v>
+        <v>-20.27038599369862</v>
       </c>
       <c r="F7">
-        <v>-2.578892598093193</v>
+        <v>-3.110692045179434</v>
       </c>
       <c r="G7">
-        <v>-1.081467768392207</v>
+        <v>-2.815401620813869</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.186683522113842</v>
       </c>
       <c r="E8">
-        <v>-18.70955933929216</v>
+        <v>-20.17017315764183</v>
       </c>
       <c r="F8">
-        <v>-2.316529589176325</v>
+        <v>-3.165000640474372</v>
       </c>
       <c r="G8">
-        <v>-0.4891159281145138</v>
+        <v>-2.443488000086826</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.1227126356541</v>
       </c>
       <c r="E9">
-        <v>-18.29237756813578</v>
+        <v>-20.75187608900864</v>
       </c>
       <c r="F9">
-        <v>-2.49616768741262</v>
+        <v>-3.249808895172985</v>
       </c>
       <c r="G9">
-        <v>-0.6769929411247992</v>
+        <v>-1.871721880910061</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.097104820523791</v>
       </c>
       <c r="E10">
-        <v>-19.96347613642776</v>
+        <v>-20.47952925638301</v>
       </c>
       <c r="F10">
-        <v>-2.632951854799889</v>
+        <v>-2.823506178670276</v>
       </c>
       <c r="G10">
-        <v>-0.4431720448001022</v>
+        <v>-1.834027950503567</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.080042649180496</v>
       </c>
       <c r="E11">
-        <v>-19.4683635079723</v>
+        <v>-21.2614086671839</v>
       </c>
       <c r="F11">
-        <v>-2.074236265694484</v>
+        <v>-2.708216488650849</v>
       </c>
       <c r="G11">
-        <v>0.2904706820040511</v>
+        <v>-1.45438913653142</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.041749794935365</v>
       </c>
       <c r="E12">
-        <v>-20.61187964167132</v>
+        <v>-21.70988903888419</v>
       </c>
       <c r="F12">
-        <v>-1.945324902103422</v>
+        <v>-2.475935641966645</v>
       </c>
       <c r="G12">
-        <v>0.03717102028505789</v>
+        <v>-0.7346512354195361</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.962756291624662</v>
       </c>
       <c r="E13">
-        <v>-20.23843949218804</v>
+        <v>-22.24535426857168</v>
       </c>
       <c r="F13">
-        <v>-2.534736473686965</v>
+        <v>-2.345564695011851</v>
       </c>
       <c r="G13">
-        <v>-0.2347354181347997</v>
+        <v>-0.03312066708607622</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.841702682972631</v>
       </c>
       <c r="E14">
-        <v>-21.42375769787145</v>
+        <v>-22.25322875724356</v>
       </c>
       <c r="F14">
-        <v>-1.462329548920517</v>
+        <v>-2.107994722460772</v>
       </c>
       <c r="G14">
-        <v>0.1240069961300769</v>
+        <v>-0.005381505805497559</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.685694900745659</v>
       </c>
       <c r="E15">
-        <v>-22.41195618765586</v>
+        <v>-23.58536298325966</v>
       </c>
       <c r="F15">
-        <v>-1.222725106028163</v>
+        <v>-2.055815031391028</v>
       </c>
       <c r="G15">
-        <v>0.5908290149778612</v>
+        <v>0.1676847531394021</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.518885552115762</v>
       </c>
       <c r="E16">
-        <v>-22.55721890695306</v>
+        <v>-23.6487659073445</v>
       </c>
       <c r="F16">
-        <v>-1.544419101803142</v>
+        <v>-1.624504005570993</v>
       </c>
       <c r="G16">
-        <v>0.687776404624262</v>
+        <v>0.5627635106233935</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.366911420666539</v>
       </c>
       <c r="E17">
-        <v>-22.9547393756977</v>
+        <v>-24.7829456219853</v>
       </c>
       <c r="F17">
-        <v>-0.8684886968342046</v>
+        <v>-1.340415404780902</v>
       </c>
       <c r="G17">
-        <v>0.6381513714363807</v>
+        <v>0.7541624180870906</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.261076839497052</v>
       </c>
       <c r="E18">
-        <v>-23.43549850581455</v>
+        <v>-24.68010380315989</v>
       </c>
       <c r="F18">
-        <v>-0.6624049692635352</v>
+        <v>-0.9842331605577683</v>
       </c>
       <c r="G18">
-        <v>0.8314221827719062</v>
+        <v>0.2562751493496493</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.222260497406114</v>
       </c>
       <c r="E19">
-        <v>-24.90341366967328</v>
+        <v>-25.69848783285315</v>
       </c>
       <c r="F19">
-        <v>-0.4268321905206062</v>
+        <v>-0.4301903919715554</v>
       </c>
       <c r="G19">
-        <v>1.549066266721717</v>
+        <v>0.552633821609874</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.267018103677171</v>
       </c>
       <c r="E20">
-        <v>-24.41530335551148</v>
+        <v>-26.84213271610324</v>
       </c>
       <c r="F20">
-        <v>-0.02138610848558259</v>
+        <v>-0.005004314727819565</v>
       </c>
       <c r="G20">
-        <v>1.188820063572359</v>
+        <v>0.7692394681007699</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.401487421148985</v>
       </c>
       <c r="E21">
-        <v>-26.70159219808237</v>
+        <v>-28.29660393490349</v>
       </c>
       <c r="F21">
-        <v>0.5690377280641818</v>
+        <v>0.4345009214407085</v>
       </c>
       <c r="G21">
-        <v>1.721748746211723</v>
+        <v>0.3363075247902271</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.621833300304623</v>
       </c>
       <c r="E22">
-        <v>-26.25200707216968</v>
+        <v>-27.8404608883089</v>
       </c>
       <c r="F22">
-        <v>1.535959519390738</v>
+        <v>0.7677133659516152</v>
       </c>
       <c r="G22">
-        <v>1.166260619560549</v>
+        <v>0.4673982321992073</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.918578821983361</v>
       </c>
       <c r="E23">
-        <v>-26.90844288811545</v>
+        <v>-28.9871106199525</v>
       </c>
       <c r="F23">
-        <v>1.1386165272899</v>
+        <v>1.094191183477762</v>
       </c>
       <c r="G23">
-        <v>0.9604399589755425</v>
+        <v>0.01916471484014955</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.270603220701019</v>
       </c>
       <c r="E24">
-        <v>-26.31929740205455</v>
+        <v>-29.07065869556842</v>
       </c>
       <c r="F24">
-        <v>1.32686964651531</v>
+        <v>1.042855598791471</v>
       </c>
       <c r="G24">
-        <v>0.5296749336756237</v>
+        <v>-0.0125427782189213</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.658697370957158</v>
       </c>
       <c r="E25">
-        <v>-26.45050150101721</v>
+        <v>-29.36590425883349</v>
       </c>
       <c r="F25">
-        <v>2.061083153577818</v>
+        <v>1.919892899975059</v>
       </c>
       <c r="G25">
-        <v>-0.833238172669156</v>
+        <v>-0.8451875506626815</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.055539498865397</v>
       </c>
       <c r="E26">
-        <v>-26.87174511284927</v>
+        <v>-29.8442566029876</v>
       </c>
       <c r="F26">
-        <v>2.32873528836156</v>
+        <v>2.07515380228177</v>
       </c>
       <c r="G26">
-        <v>-0.3126504797119846</v>
+        <v>-1.119125148374425</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.43988673345199</v>
       </c>
       <c r="E27">
-        <v>-27.92472123966702</v>
+        <v>-30.71534076322883</v>
       </c>
       <c r="F27">
-        <v>1.681291610007495</v>
+        <v>2.125662676300067</v>
       </c>
       <c r="G27">
-        <v>-0.8141588511973001</v>
+        <v>-1.054963489303225</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.790271099616691</v>
       </c>
       <c r="E28">
-        <v>-27.67820738148182</v>
+        <v>-29.96165127429521</v>
       </c>
       <c r="F28">
-        <v>2.323012926343021</v>
+        <v>1.900353369677824</v>
       </c>
       <c r="G28">
-        <v>-0.6068291802386296</v>
+        <v>-1.386068561326576</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.088689934247902</v>
       </c>
       <c r="E29">
-        <v>-26.6148814520426</v>
+        <v>-30.29531196570928</v>
       </c>
       <c r="F29">
-        <v>2.117637452901746</v>
+        <v>2.088854999124074</v>
       </c>
       <c r="G29">
-        <v>-0.8001835354010707</v>
+        <v>-1.584571304822693</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.323943739235845</v>
       </c>
       <c r="E30">
-        <v>-28.08016347992138</v>
+        <v>-30.06197001724078</v>
       </c>
       <c r="F30">
-        <v>2.522016597721963</v>
+        <v>2.187573199250497</v>
       </c>
       <c r="G30">
-        <v>-1.000764431591713</v>
+        <v>-1.914250910299296</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.483907733025291</v>
       </c>
       <c r="E31">
-        <v>-27.46442082853627</v>
+        <v>-29.87822364180771</v>
       </c>
       <c r="F31">
-        <v>1.557251875112297</v>
+        <v>2.312941635459785</v>
       </c>
       <c r="G31">
-        <v>0.2964022937150605</v>
+        <v>-1.328650455534222</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.564607880975495</v>
       </c>
       <c r="E32">
-        <v>-27.20201678382228</v>
+        <v>-29.97286286826658</v>
       </c>
       <c r="F32">
-        <v>1.90123972279882</v>
+        <v>1.858312067250944</v>
       </c>
       <c r="G32">
-        <v>-0.7648732148062635</v>
+        <v>-1.47894318941084</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.561996074334649</v>
       </c>
       <c r="E33">
-        <v>-26.48448307607696</v>
+        <v>-28.80447730515449</v>
       </c>
       <c r="F33">
-        <v>1.946723720151735</v>
+        <v>1.724746107223551</v>
       </c>
       <c r="G33">
-        <v>-0.4717596980727927</v>
+        <v>-1.405027788547241</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.475505562090341</v>
       </c>
       <c r="E34">
-        <v>-26.83881014704338</v>
+        <v>-28.8161291395263</v>
       </c>
       <c r="F34">
-        <v>1.164045749821039</v>
+        <v>1.619024889073862</v>
       </c>
       <c r="G34">
-        <v>-0.5456072195770231</v>
+        <v>-1.575556403749579</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.30963651439518</v>
       </c>
       <c r="E35">
-        <v>-25.4889500150929</v>
+        <v>-28.98088495617658</v>
       </c>
       <c r="F35">
-        <v>1.450867963040368</v>
+        <v>1.268827599335954</v>
       </c>
       <c r="G35">
-        <v>-0.5422602450112158</v>
+        <v>-1.660439542640445</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.066452118337632</v>
       </c>
       <c r="E36">
-        <v>-24.67565156061968</v>
+        <v>-27.86587854161685</v>
       </c>
       <c r="F36">
-        <v>1.398768623608695</v>
+        <v>1.550805519983711</v>
       </c>
       <c r="G36">
-        <v>-0.4235992926005259</v>
+        <v>-1.133512961816051</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.754380900171192</v>
       </c>
       <c r="E37">
-        <v>-24.95206023392099</v>
+        <v>-27.85376362418233</v>
       </c>
       <c r="F37">
-        <v>0.386117638177995</v>
+        <v>1.136416383468064</v>
       </c>
       <c r="G37">
-        <v>0.6066214090095056</v>
+        <v>-0.7992880500063189</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.380426709613971</v>
       </c>
       <c r="E38">
-        <v>-25.98534598584774</v>
+        <v>-26.94088777498501</v>
       </c>
       <c r="F38">
-        <v>0.8143189727679211</v>
+        <v>0.9486089259053601</v>
       </c>
       <c r="G38">
-        <v>0.893181956819282</v>
+        <v>-1.045092264004226</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.952380925168379</v>
       </c>
       <c r="E39">
-        <v>-23.74872124429914</v>
+        <v>-26.4015060670182</v>
       </c>
       <c r="F39">
-        <v>1.307929854217702</v>
+        <v>0.714726016664142</v>
       </c>
       <c r="G39">
-        <v>0.6035981667729964</v>
+        <v>-0.228542731964679</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.483769888881697</v>
       </c>
       <c r="E40">
-        <v>-23.09201546961726</v>
+        <v>-26.13636920925248</v>
       </c>
       <c r="F40">
-        <v>0.6322164815082973</v>
+        <v>0.6157187163141423</v>
       </c>
       <c r="G40">
-        <v>0.7775129177100079</v>
+        <v>0.435288684473105</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.98271352190157</v>
       </c>
       <c r="E41">
-        <v>-24.0071880446772</v>
+        <v>-25.29490782878559</v>
       </c>
       <c r="F41">
-        <v>0.3483656221628104</v>
+        <v>0.6226306139231015</v>
       </c>
       <c r="G41">
-        <v>1.625208632721536</v>
+        <v>0.02785327283937457</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.467622593148571</v>
       </c>
       <c r="E42">
-        <v>-23.04615986337982</v>
+        <v>-26.27551840147953</v>
       </c>
       <c r="F42">
-        <v>0.5212102793287468</v>
+        <v>0.2633436486742747</v>
       </c>
       <c r="G42">
-        <v>1.628934165253055</v>
+        <v>0.2249331605333343</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.949914980466319</v>
       </c>
       <c r="E43">
-        <v>-21.89190767840613</v>
+        <v>-24.203435586198</v>
       </c>
       <c r="F43">
-        <v>-0.3601146515317312</v>
+        <v>-0.2821263456603662</v>
       </c>
       <c r="G43">
-        <v>0.9848713068591806</v>
+        <v>0.8400350291779889</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.447443145061069</v>
       </c>
       <c r="E44">
-        <v>-23.94587003267743</v>
+        <v>-23.83674025190624</v>
       </c>
       <c r="F44">
-        <v>0.2341470111952033</v>
+        <v>0.006402304408729627</v>
       </c>
       <c r="G44">
-        <v>2.73469937235154</v>
+        <v>0.7854469705224012</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.976174708804769</v>
       </c>
       <c r="E45">
-        <v>-22.0323983578911</v>
+        <v>-24.7060489143061</v>
       </c>
       <c r="F45">
-        <v>-0.5210738932023004</v>
+        <v>-0.4117045450106817</v>
       </c>
       <c r="G45">
-        <v>1.657545315227065</v>
+        <v>1.375227227377848</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.548609167042682</v>
       </c>
       <c r="E46">
-        <v>-20.24446580182036</v>
+        <v>-23.92322672453447</v>
       </c>
       <c r="F46">
-        <v>0.2260903098355753</v>
+        <v>-0.1706148393651079</v>
       </c>
       <c r="G46">
-        <v>1.661732949551211</v>
+        <v>0.8750346711664536</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.18116565130621</v>
       </c>
       <c r="E47">
-        <v>-19.84636388349025</v>
+        <v>-22.94387457487195</v>
       </c>
       <c r="F47">
-        <v>-0.3406123977676225</v>
+        <v>-0.376295152010614</v>
       </c>
       <c r="G47">
-        <v>2.735769777633897</v>
+        <v>0.5056117007793325</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.881578321161718</v>
       </c>
       <c r="E48">
-        <v>-20.97049697993629</v>
+        <v>-22.82618087234896</v>
       </c>
       <c r="F48">
-        <v>-0.5021987135621109</v>
+        <v>-0.6113493727593905</v>
       </c>
       <c r="G48">
-        <v>2.088179803297428</v>
+        <v>0.8114003825026583</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.661986607634004</v>
       </c>
       <c r="E49">
-        <v>-20.16096964134601</v>
+        <v>-22.36465941708871</v>
       </c>
       <c r="F49">
-        <v>0.3671372558776499</v>
+        <v>-0.4976385510096996</v>
       </c>
       <c r="G49">
-        <v>1.483262449302707</v>
+        <v>0.5926043212998183</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.525609083910672</v>
       </c>
       <c r="E50">
-        <v>-20.43120664261863</v>
+        <v>-21.26418716556022</v>
       </c>
       <c r="F50">
-        <v>-0.08850209219520414</v>
+        <v>-0.9587476090432387</v>
       </c>
       <c r="G50">
-        <v>0.9667214104617611</v>
+        <v>1.107388329030945</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.476725902353839</v>
       </c>
       <c r="E51">
-        <v>-18.64987353934304</v>
+        <v>-22.1759042687979</v>
       </c>
       <c r="F51">
-        <v>0.03817267940829906</v>
+        <v>-0.8467962396570939</v>
       </c>
       <c r="G51">
-        <v>1.918460518918336</v>
+        <v>0.8591456795849381</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.512884301234194</v>
       </c>
       <c r="E52">
-        <v>-19.17015878163829</v>
+        <v>-20.39937227781382</v>
       </c>
       <c r="F52">
-        <v>-0.1170608867741199</v>
+        <v>-1.004151254758082</v>
       </c>
       <c r="G52">
-        <v>2.05774374285423</v>
+        <v>0.6414513525995479</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.629669249485668</v>
       </c>
       <c r="E53">
-        <v>-18.20421735134364</v>
+        <v>-20.97278539937627</v>
       </c>
       <c r="F53">
-        <v>-0.07132092389373959</v>
+        <v>-1.084656969166555</v>
       </c>
       <c r="G53">
-        <v>1.043960289189848</v>
+        <v>0.6809493075185008</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.818833137469371</v>
       </c>
       <c r="E54">
-        <v>-18.28175780677819</v>
+        <v>-20.93066768333118</v>
       </c>
       <c r="F54">
-        <v>0.03946244745445789</v>
+        <v>-1.06454338025918</v>
       </c>
       <c r="G54">
-        <v>0.9431881587174659</v>
+        <v>0.5559651317081344</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.069632482898037</v>
       </c>
       <c r="E55">
-        <v>-17.91813169565548</v>
+        <v>-20.31953509651664</v>
       </c>
       <c r="F55">
-        <v>-0.9444731819581976</v>
+        <v>-0.9784619248624642</v>
       </c>
       <c r="G55">
-        <v>0.695358006916855</v>
+        <v>0.2200928400614102</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.36966218347627</v>
       </c>
       <c r="E56">
-        <v>-16.8773286312308</v>
+        <v>-19.23788104550095</v>
       </c>
       <c r="F56">
-        <v>-0.582318408760879</v>
+        <v>-1.567136249457516</v>
       </c>
       <c r="G56">
-        <v>0.8158099301170487</v>
+        <v>-0.4616300090592731</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.70299062786212</v>
       </c>
       <c r="E57">
-        <v>-17.08827854084149</v>
+        <v>-19.85316684364032</v>
       </c>
       <c r="F57">
-        <v>-1.016691908869064</v>
+        <v>-1.294747509864566</v>
       </c>
       <c r="G57">
-        <v>0.3077538111972211</v>
+        <v>-0.4386815641033874</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.057590128437394</v>
       </c>
       <c r="E58">
-        <v>-16.3479686221908</v>
+        <v>-19.32810540832152</v>
       </c>
       <c r="F58">
-        <v>-0.9363460693693317</v>
+        <v>-1.239863199224682</v>
       </c>
       <c r="G58">
-        <v>1.196406887354134</v>
+        <v>-0.7880618482645317</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.417181683791868</v>
       </c>
       <c r="E59">
-        <v>-15.16883454817005</v>
+        <v>-19.76341179369945</v>
       </c>
       <c r="F59">
-        <v>-1.448403036144652</v>
+        <v>-1.630465765768941</v>
       </c>
       <c r="G59">
-        <v>-0.2047745132071837</v>
+        <v>-0.3479216391379251</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.774105499740489</v>
       </c>
       <c r="E60">
-        <v>-16.75042725920066</v>
+        <v>-19.60848039843804</v>
       </c>
       <c r="F60">
-        <v>-1.949325916658944</v>
+        <v>-1.619110505411365</v>
       </c>
       <c r="G60">
-        <v>-0.4692559940099151</v>
+        <v>-0.5182178980716536</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.11697093087178</v>
       </c>
       <c r="E61">
-        <v>-15.27899017213848</v>
+        <v>-19.25411179535837</v>
       </c>
       <c r="F61">
-        <v>-1.476898874800955</v>
+        <v>-1.612795860699825</v>
       </c>
       <c r="G61">
-        <v>-1.285554894568715</v>
+        <v>-1.513352803121714</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.442146308841416</v>
       </c>
       <c r="E62">
-        <v>-18.00610086472667</v>
+        <v>-18.4190255942751</v>
       </c>
       <c r="F62">
-        <v>-1.028744654579797</v>
+        <v>-1.995841231428344</v>
       </c>
       <c r="G62">
-        <v>-0.6601562492567096</v>
+        <v>-1.426253142072992</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.746396383449381</v>
       </c>
       <c r="E63">
-        <v>-16.51838318927116</v>
+        <v>-18.8313771806607</v>
       </c>
       <c r="F63">
-        <v>-1.381109781810831</v>
+        <v>-1.953554732250235</v>
       </c>
       <c r="G63">
-        <v>-1.096949483817509</v>
+        <v>-1.263441887881986</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.027027205234084</v>
       </c>
       <c r="E64">
-        <v>-15.44658055551796</v>
+        <v>-17.73213843289568</v>
       </c>
       <c r="F64">
-        <v>-1.025446923949252</v>
+        <v>-2.198746513274472</v>
       </c>
       <c r="G64">
-        <v>-1.787744670392311</v>
+        <v>-1.612104217280574</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.287431408641937</v>
       </c>
       <c r="E65">
-        <v>-15.30357718318146</v>
+        <v>-17.78210571834469</v>
       </c>
       <c r="F65">
-        <v>-1.633934140084463</v>
+        <v>-2.277670045943597</v>
       </c>
       <c r="G65">
-        <v>-0.624258511128902</v>
+        <v>-2.019847696776055</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.524796989181108</v>
       </c>
       <c r="E66">
-        <v>-15.34009637036068</v>
+        <v>-19.06754123622443</v>
       </c>
       <c r="F66">
-        <v>-1.811637172067818</v>
+        <v>-2.09500426485007</v>
       </c>
       <c r="G66">
-        <v>-0.4762554002586898</v>
+        <v>-1.881091843247567</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.743453775561941</v>
       </c>
       <c r="E67">
-        <v>-15.29656656246515</v>
+        <v>-17.99524021711224</v>
       </c>
       <c r="F67">
-        <v>-2.641415284554291</v>
+        <v>-2.687798060539244</v>
       </c>
       <c r="G67">
-        <v>-0.8263901896066659</v>
+        <v>-1.847358412385792</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.941944421033895</v>
       </c>
       <c r="E68">
-        <v>-16.2868790368139</v>
+        <v>-17.90634488191562</v>
       </c>
       <c r="F68">
-        <v>-1.772626865967781</v>
+        <v>-2.473867208561855</v>
       </c>
       <c r="G68">
-        <v>-1.717241512709297</v>
+        <v>-2.038699883468484</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.120975120310483</v>
       </c>
       <c r="E69">
-        <v>-15.30958272675717</v>
+        <v>-17.92918754420217</v>
       </c>
       <c r="F69">
-        <v>-1.904637152012716</v>
+        <v>-2.61205297359466</v>
       </c>
       <c r="G69">
-        <v>-1.600421135235342</v>
+        <v>-2.181113390169123</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.280961209220609</v>
       </c>
       <c r="E70">
-        <v>-15.77595513284481</v>
+        <v>-17.42804860611438</v>
       </c>
       <c r="F70">
-        <v>-1.943717869341991</v>
+        <v>-2.429933086619577</v>
       </c>
       <c r="G70">
-        <v>-2.321117179612164</v>
+        <v>-2.510174249177633</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.418194997796474</v>
       </c>
       <c r="E71">
-        <v>-16.51640210746922</v>
+        <v>-17.63344151897245</v>
       </c>
       <c r="F71">
-        <v>-2.541093365136049</v>
+        <v>-2.900053953628173</v>
       </c>
       <c r="G71">
-        <v>-0.2604460308680833</v>
+        <v>-2.62641243060777</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.533831001275632</v>
       </c>
       <c r="E72">
-        <v>-16.02596599496552</v>
+        <v>-18.25638168558349</v>
       </c>
       <c r="F72">
-        <v>-2.029043853667354</v>
+        <v>-3.019427494943401</v>
       </c>
       <c r="G72">
-        <v>-0.7277275407639037</v>
+        <v>-2.567352166467605</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.623038688548562</v>
       </c>
       <c r="E73">
-        <v>-18.40002880567533</v>
+        <v>-17.87317318306421</v>
       </c>
       <c r="F73">
-        <v>-2.441830099258584</v>
+        <v>-2.792694224755746</v>
       </c>
       <c r="G73">
-        <v>-0.8075510566371924</v>
+        <v>-2.57604072446683</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.685393779958066</v>
       </c>
       <c r="E74">
-        <v>-15.97707854446096</v>
+        <v>-18.20094046760835</v>
       </c>
       <c r="F74">
-        <v>-2.232637508825208</v>
+        <v>-3.047895169108009</v>
       </c>
       <c r="G74">
-        <v>-2.48385533295462</v>
+        <v>-3.041904600049676</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.720366408840738</v>
       </c>
       <c r="E75">
-        <v>-16.73245631379812</v>
+        <v>-18.62961002128921</v>
       </c>
       <c r="F75">
-        <v>-2.364531823433751</v>
+        <v>-3.057408968729161</v>
       </c>
       <c r="G75">
-        <v>-1.355640333117151</v>
+        <v>-3.116279491961311</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.726574267746701</v>
       </c>
       <c r="E76">
-        <v>-18.07736166463808</v>
+        <v>-18.83197108988015</v>
       </c>
       <c r="F76">
-        <v>-2.518936193845968</v>
+        <v>-2.587359341317207</v>
       </c>
       <c r="G76">
-        <v>-1.100064102114707</v>
+        <v>-2.762669801562563</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.70770332260556</v>
       </c>
       <c r="E77">
-        <v>-16.69643135876656</v>
+        <v>-19.11353389843558</v>
       </c>
       <c r="F77">
-        <v>-2.248755881748881</v>
+        <v>-2.729933796850044</v>
       </c>
       <c r="G77">
-        <v>-1.85363986387201</v>
+        <v>-2.812890084517218</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.663809689042704</v>
       </c>
       <c r="E78">
-        <v>-17.69562755213911</v>
+        <v>-20.20187877289557</v>
       </c>
       <c r="F78">
-        <v>-2.920082220693059</v>
+        <v>-3.028754083531521</v>
       </c>
       <c r="G78">
-        <v>-0.3531614035322895</v>
+        <v>-2.237607292376223</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.601445385205732</v>
       </c>
       <c r="E79">
-        <v>-17.43512152500057</v>
+        <v>-20.22840533362725</v>
       </c>
       <c r="F79">
-        <v>-2.968733066626877</v>
+        <v>-2.718947159986714</v>
       </c>
       <c r="G79">
-        <v>-0.5415762299283442</v>
+        <v>-2.313076086271535</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.524315522366164</v>
       </c>
       <c r="E80">
-        <v>-18.9149647117842</v>
+        <v>-20.99588556076497</v>
       </c>
       <c r="F80">
-        <v>-2.369208785789957</v>
+        <v>-3.002382178895996</v>
       </c>
       <c r="G80">
-        <v>-0.03142890459103481</v>
+        <v>-2.59897611569976</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.43907141483222</v>
       </c>
       <c r="E81">
-        <v>-19.59235347886374</v>
+        <v>-22.27784899397714</v>
       </c>
       <c r="F81">
-        <v>-2.387282105784236</v>
+        <v>-3.00957986325892</v>
       </c>
       <c r="G81">
-        <v>0.2187091454281202</v>
+        <v>-2.349164408754494</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.354239527052804</v>
       </c>
       <c r="E82">
-        <v>-21.31039994797158</v>
+        <v>-23.24550570054895</v>
       </c>
       <c r="F82">
-        <v>-2.239222201310061</v>
+        <v>-2.733029405834305</v>
       </c>
       <c r="G82">
-        <v>-0.1422732876959316</v>
+        <v>-2.728093100197859</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.27513859467524</v>
       </c>
       <c r="E83">
-        <v>-22.30911436883045</v>
+        <v>-24.63956430741824</v>
       </c>
       <c r="F83">
-        <v>-2.841727776429657</v>
+        <v>-2.472653650316754</v>
       </c>
       <c r="G83">
-        <v>1.089825850166526</v>
+        <v>-1.872912380443609</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.212759194671603</v>
       </c>
       <c r="E84">
-        <v>-22.27350058172005</v>
+        <v>-24.84260234945514</v>
       </c>
       <c r="F84">
-        <v>-2.632106091681631</v>
+        <v>-2.615451765048346</v>
       </c>
       <c r="G84">
-        <v>0.07211061514792699</v>
+        <v>-2.41535722711758</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.171673933908987</v>
       </c>
       <c r="E85">
-        <v>-23.44599367083239</v>
+        <v>-25.9631761437958</v>
       </c>
       <c r="F85">
-        <v>-2.518820222409575</v>
+        <v>-2.718450967912437</v>
       </c>
       <c r="G85">
-        <v>-0.3257746927715111</v>
+        <v>-2.124115614255938</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.163378002534468</v>
       </c>
       <c r="E86">
-        <v>-23.43451834794189</v>
+        <v>-27.00280800262688</v>
       </c>
       <c r="F86">
-        <v>-2.81421603824788</v>
+        <v>-2.084201525550162</v>
       </c>
       <c r="G86">
-        <v>0.6877424649445776</v>
+        <v>-1.621121729098279</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.192622623771691</v>
       </c>
       <c r="E87">
-        <v>-24.81232128568581</v>
+        <v>-28.40272679067551</v>
       </c>
       <c r="F87">
-        <v>-2.488839949367456</v>
+        <v>-2.113611881819156</v>
       </c>
       <c r="G87">
-        <v>0.7649996188848019</v>
+        <v>-1.655787195779081</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.270106923265354</v>
       </c>
       <c r="E88">
-        <v>-26.60610986972456</v>
+        <v>-28.68125567835815</v>
       </c>
       <c r="F88">
-        <v>-2.176382250133691</v>
+        <v>-1.864353645214576</v>
       </c>
       <c r="G88">
-        <v>-0.2744213466643128</v>
+        <v>-1.904277865961244</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.404208518557982</v>
       </c>
       <c r="E89">
-        <v>-28.80462266755086</v>
+        <v>-30.79946198200757</v>
       </c>
       <c r="F89">
-        <v>-2.556073561248275</v>
+        <v>-1.882893336056632</v>
       </c>
       <c r="G89">
-        <v>0.3163118319668904</v>
+        <v>-1.770793105762213</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.599940068975894</v>
       </c>
       <c r="E90">
-        <v>-30.54911263316389</v>
+        <v>-32.0734387898421</v>
       </c>
       <c r="F90">
-        <v>-2.070858183425867</v>
+        <v>-1.897354145807303</v>
       </c>
       <c r="G90">
-        <v>0.6842414564478947</v>
+        <v>-2.46584641676512</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.867449011997097</v>
       </c>
       <c r="E91">
-        <v>-33.47967668892146</v>
+        <v>-33.68361597781584</v>
       </c>
       <c r="F91">
-        <v>-2.46085521339868</v>
+        <v>-1.871791556124313</v>
       </c>
       <c r="G91">
-        <v>1.017735359772115</v>
+        <v>-1.752878176377993</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.205230051362867</v>
       </c>
       <c r="E92">
-        <v>-34.61045700009289</v>
+        <v>-35.6579218154826</v>
       </c>
       <c r="F92">
-        <v>-1.677163321366958</v>
+        <v>-1.578166789793194</v>
       </c>
       <c r="G92">
-        <v>0.7581829647574051</v>
+        <v>-2.08906114663106</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.621471781845108</v>
       </c>
       <c r="E93">
-        <v>-37.21224246434871</v>
+        <v>-37.54522618231685</v>
       </c>
       <c r="F93">
-        <v>-1.689255828713025</v>
+        <v>-0.9894974354025592</v>
       </c>
       <c r="G93">
-        <v>0.2432397016062206</v>
+        <v>-2.235330723092773</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.107717474537063</v>
       </c>
       <c r="E94">
-        <v>-35.82883061471061</v>
+        <v>-39.74302047458395</v>
       </c>
       <c r="F94">
-        <v>-2.131324861993217</v>
+        <v>-1.38492938390514</v>
       </c>
       <c r="G94">
-        <v>0.1560251677954902</v>
+        <v>-2.791542025995685</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.66313636901171</v>
       </c>
       <c r="E95">
-        <v>-40.23182022182567</v>
+        <v>-42.37235834276868</v>
       </c>
       <c r="F95">
-        <v>-2.31023151181284</v>
+        <v>-1.301144991316386</v>
       </c>
       <c r="G95">
-        <v>-0.04582977175561569</v>
+        <v>-3.103805354304972</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.281449651326923</v>
       </c>
       <c r="E96">
-        <v>-41.81645723675737</v>
+        <v>-43.67610744598525</v>
       </c>
       <c r="F96">
-        <v>-2.109071600084412</v>
+        <v>-1.229248499325209</v>
       </c>
       <c r="G96">
-        <v>-1.164492057134201</v>
+        <v>-2.376934898970166</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.940975547318127</v>
       </c>
       <c r="E97">
-        <v>-44.34655827354666</v>
+        <v>-45.83641173792596</v>
       </c>
       <c r="F97">
-        <v>-1.684412364508856</v>
+        <v>-0.9040770171932769</v>
       </c>
       <c r="G97">
-        <v>-0.2758102627867851</v>
+        <v>-2.525259131425085</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.6419849897509</v>
       </c>
       <c r="E98">
-        <v>-46.32406312223637</v>
+        <v>-47.41267068731266</v>
       </c>
       <c r="F98">
-        <v>-2.019397515261754</v>
+        <v>-0.8071141275933864</v>
       </c>
       <c r="G98">
-        <v>-1.08761868264887</v>
+        <v>-2.925133826722952</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.3419605061971</v>
       </c>
       <c r="E99">
-        <v>-48.96385877653702</v>
+        <v>-49.99499108839184</v>
       </c>
       <c r="F99">
-        <v>-1.864825814634172</v>
+        <v>-0.4475107259966903</v>
       </c>
       <c r="G99">
-        <v>-1.194687929075017</v>
+        <v>-3.254604572632266</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.05507022151652</v>
       </c>
       <c r="E100">
-        <v>-50.91551819115232</v>
+        <v>-52.12826005121358</v>
       </c>
       <c r="F100">
-        <v>-2.064428395645338</v>
+        <v>-0.8058997409808824</v>
       </c>
       <c r="G100">
-        <v>-1.110642839197898</v>
+        <v>-2.838297850877933</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.71085629916616</v>
       </c>
       <c r="E101">
-        <v>-52.48323294654102</v>
+        <v>-53.80704829027349</v>
       </c>
       <c r="F101">
-        <v>-2.191799824234595</v>
+        <v>-0.4726831546329616</v>
       </c>
       <c r="G101">
-        <v>-1.948258469343138</v>
+        <v>-3.131604562711146</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.36859654584734</v>
       </c>
       <c r="E102">
-        <v>-53.41528728733356</v>
+        <v>-55.5946205552618</v>
       </c>
       <c r="F102">
-        <v>-1.739866591921866</v>
+        <v>-0.7748359633759009</v>
       </c>
       <c r="G102">
-        <v>-1.553957713747299</v>
+        <v>-3.802581587094807</v>
       </c>
     </row>
   </sheetData>
